--- a/data/raw/sniim/sniim_producto_133_2026-03-03_2026-03-16.xlsx
+++ b/data/raw/sniim/sniim_producto_133_2026-03-03_2026-03-16.xlsx
@@ -466,47 +466,47 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>observaciones</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>fecha_inicio_query</t>
+          <t>fecha_inicio_consulta</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>fecha_final_query</t>
+          <t>fecha_fin_consulta</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>producto_id</t>
+          <t>id_producto</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>origen_id</t>
+          <t>id_origen</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>destino_id</t>
+          <t>id_destino</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>origen_query</t>
+          <t>origen_consulta</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>destino_query</t>
+          <t>destino_consulta</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>precios_por_id</t>
+          <t>id_precios_por</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -575,15 +575,11 @@
       <c r="M2" t="n">
         <v>-1</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-1</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -650,15 +646,11 @@
       <c r="M3" t="n">
         <v>-1</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -725,15 +717,11 @@
       <c r="M4" t="n">
         <v>-1</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -800,15 +788,11 @@
       <c r="M5" t="n">
         <v>-1</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -875,15 +859,11 @@
       <c r="M6" t="n">
         <v>-1</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -950,15 +930,11 @@
       <c r="M7" t="n">
         <v>-1</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1025,15 +1001,11 @@
       <c r="M8" t="n">
         <v>-1</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1100,15 +1072,11 @@
       <c r="M9" t="n">
         <v>-1</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1175,15 +1143,11 @@
       <c r="M10" t="n">
         <v>-1</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1250,15 +1214,11 @@
       <c r="M11" t="n">
         <v>-1</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1325,15 +1285,11 @@
       <c r="M12" t="n">
         <v>-1</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -1400,15 +1356,11 @@
       <c r="M13" t="n">
         <v>-1</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1475,15 +1427,11 @@
       <c r="M14" t="n">
         <v>-1</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1550,15 +1498,11 @@
       <c r="M15" t="n">
         <v>-1</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1625,15 +1569,11 @@
       <c r="M16" t="n">
         <v>-1</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -1700,15 +1640,11 @@
       <c r="M17" t="n">
         <v>-1</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1775,15 +1711,11 @@
       <c r="M18" t="n">
         <v>-1</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1850,15 +1782,11 @@
       <c r="M19" t="n">
         <v>-1</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -1925,15 +1853,11 @@
       <c r="M20" t="n">
         <v>-1</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -2000,15 +1924,11 @@
       <c r="M21" t="n">
         <v>-1</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -2075,15 +1995,11 @@
       <c r="M22" t="n">
         <v>-1</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -2150,15 +2066,11 @@
       <c r="M23" t="n">
         <v>-1</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -2225,15 +2137,11 @@
       <c r="M24" t="n">
         <v>-1</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
@@ -2300,15 +2208,11 @@
       <c r="M25" t="n">
         <v>-1</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
@@ -2375,15 +2279,11 @@
       <c r="M26" t="n">
         <v>-1</v>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -2450,15 +2350,11 @@
       <c r="M27" t="n">
         <v>-1</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2525,15 +2421,11 @@
       <c r="M28" t="n">
         <v>-1</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-1</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -2600,15 +2492,11 @@
       <c r="M29" t="n">
         <v>-1</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-1</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -2675,15 +2563,11 @@
       <c r="M30" t="n">
         <v>-1</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2750,15 +2634,11 @@
       <c r="M31" t="n">
         <v>-1</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
@@ -2825,15 +2705,11 @@
       <c r="M32" t="n">
         <v>-1</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-1</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
@@ -2900,15 +2776,11 @@
       <c r="M33" t="n">
         <v>-1</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2975,15 +2847,11 @@
       <c r="M34" t="n">
         <v>-1</v>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-1</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
@@ -3050,15 +2918,11 @@
       <c r="M35" t="n">
         <v>-1</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-1</v>
       </c>
       <c r="P35" t="n">
         <v>2</v>
@@ -3125,15 +2989,11 @@
       <c r="M36" t="n">
         <v>-1</v>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -3200,15 +3060,11 @@
       <c r="M37" t="n">
         <v>-1</v>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-1</v>
       </c>
       <c r="P37" t="n">
         <v>2</v>
@@ -3275,15 +3131,11 @@
       <c r="M38" t="n">
         <v>-1</v>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-1</v>
       </c>
       <c r="P38" t="n">
         <v>2</v>
@@ -3350,15 +3202,11 @@
       <c r="M39" t="n">
         <v>-1</v>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-1</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3425,15 +3273,11 @@
       <c r="M40" t="n">
         <v>-1</v>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-1</v>
       </c>
       <c r="P40" t="n">
         <v>2</v>
@@ -3500,15 +3344,11 @@
       <c r="M41" t="n">
         <v>-1</v>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-1</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
@@ -3575,15 +3415,11 @@
       <c r="M42" t="n">
         <v>-1</v>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-1</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3650,15 +3486,11 @@
       <c r="M43" t="n">
         <v>-1</v>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-1</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
@@ -3725,15 +3557,11 @@
       <c r="M44" t="n">
         <v>-1</v>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-1</v>
       </c>
       <c r="P44" t="n">
         <v>2</v>
@@ -3800,15 +3628,11 @@
       <c r="M45" t="n">
         <v>-1</v>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-1</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3875,15 +3699,11 @@
       <c r="M46" t="n">
         <v>-1</v>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-1</v>
       </c>
       <c r="P46" t="n">
         <v>2</v>
@@ -3950,15 +3770,11 @@
       <c r="M47" t="n">
         <v>-1</v>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-1</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
@@ -4025,15 +3841,11 @@
       <c r="M48" t="n">
         <v>-1</v>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-1</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -4100,15 +3912,11 @@
       <c r="M49" t="n">
         <v>-1</v>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-1</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -4175,15 +3983,11 @@
       <c r="M50" t="n">
         <v>-1</v>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-1</v>
       </c>
       <c r="P50" t="n">
         <v>2</v>
@@ -4250,15 +4054,11 @@
       <c r="M51" t="n">
         <v>-1</v>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-1</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
@@ -4325,15 +4125,11 @@
       <c r="M52" t="n">
         <v>-1</v>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-1</v>
       </c>
       <c r="P52" t="n">
         <v>2</v>
@@ -4400,15 +4196,11 @@
       <c r="M53" t="n">
         <v>-1</v>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-1</v>
       </c>
       <c r="P53" t="n">
         <v>2</v>
@@ -4475,15 +4267,11 @@
       <c r="M54" t="n">
         <v>-1</v>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-1</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -4550,15 +4338,11 @@
       <c r="M55" t="n">
         <v>-1</v>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-1</v>
       </c>
       <c r="P55" t="n">
         <v>2</v>
@@ -4625,15 +4409,11 @@
       <c r="M56" t="n">
         <v>-1</v>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-1</v>
       </c>
       <c r="P56" t="n">
         <v>2</v>
@@ -4700,15 +4480,11 @@
       <c r="M57" t="n">
         <v>-1</v>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-1</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -4775,15 +4551,11 @@
       <c r="M58" t="n">
         <v>-1</v>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-1</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
@@ -4850,15 +4622,11 @@
       <c r="M59" t="n">
         <v>-1</v>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-1</v>
       </c>
       <c r="P59" t="n">
         <v>2</v>
@@ -4925,15 +4693,11 @@
       <c r="M60" t="n">
         <v>-1</v>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-1</v>
       </c>
       <c r="P60" t="n">
         <v>2</v>
@@ -5000,15 +4764,11 @@
       <c r="M61" t="n">
         <v>-1</v>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-1</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
@@ -5075,15 +4835,11 @@
       <c r="M62" t="n">
         <v>-1</v>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-1</v>
       </c>
       <c r="P62" t="n">
         <v>2</v>
@@ -5150,15 +4906,11 @@
       <c r="M63" t="n">
         <v>-1</v>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-1</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -5225,15 +4977,11 @@
       <c r="M64" t="n">
         <v>-1</v>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-1</v>
       </c>
       <c r="P64" t="n">
         <v>2</v>
@@ -5300,15 +5048,11 @@
       <c r="M65" t="n">
         <v>-1</v>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-1</v>
       </c>
       <c r="P65" t="n">
         <v>2</v>
@@ -5375,15 +5119,11 @@
       <c r="M66" t="n">
         <v>-1</v>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-1</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
@@ -5450,15 +5190,11 @@
       <c r="M67" t="n">
         <v>-1</v>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-1</v>
       </c>
       <c r="P67" t="n">
         <v>2</v>
@@ -5525,15 +5261,11 @@
       <c r="M68" t="n">
         <v>-1</v>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-1</v>
       </c>
       <c r="P68" t="n">
         <v>2</v>
@@ -5600,15 +5332,11 @@
       <c r="M69" t="n">
         <v>-1</v>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-1</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5675,15 +5403,11 @@
       <c r="M70" t="n">
         <v>-1</v>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-1</v>
       </c>
       <c r="P70" t="n">
         <v>2</v>
@@ -5750,15 +5474,11 @@
       <c r="M71" t="n">
         <v>-1</v>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-1</v>
       </c>
       <c r="P71" t="n">
         <v>2</v>
@@ -5825,15 +5545,11 @@
       <c r="M72" t="n">
         <v>-1</v>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-1</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5900,15 +5616,11 @@
       <c r="M73" t="n">
         <v>-1</v>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-1</v>
       </c>
       <c r="P73" t="n">
         <v>2</v>
@@ -5975,15 +5687,11 @@
       <c r="M74" t="n">
         <v>-1</v>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>-1</v>
       </c>
       <c r="P74" t="n">
         <v>2</v>
@@ -6050,15 +5758,11 @@
       <c r="M75" t="n">
         <v>-1</v>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-1</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -6125,15 +5829,11 @@
       <c r="M76" t="n">
         <v>-1</v>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-1</v>
       </c>
       <c r="P76" t="n">
         <v>2</v>
@@ -6200,15 +5900,11 @@
       <c r="M77" t="n">
         <v>-1</v>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-1</v>
       </c>
       <c r="P77" t="n">
         <v>2</v>
@@ -6275,15 +5971,11 @@
       <c r="M78" t="n">
         <v>-1</v>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-1</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
@@ -6350,15 +6042,11 @@
       <c r="M79" t="n">
         <v>-1</v>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-1</v>
       </c>
       <c r="P79" t="n">
         <v>2</v>
@@ -6425,15 +6113,11 @@
       <c r="M80" t="n">
         <v>-1</v>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-1</v>
       </c>
       <c r="P80" t="n">
         <v>2</v>
@@ -6500,15 +6184,11 @@
       <c r="M81" t="n">
         <v>-1</v>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-1</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -6575,15 +6255,11 @@
       <c r="M82" t="n">
         <v>-1</v>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-1</v>
       </c>
       <c r="P82" t="n">
         <v>2</v>
@@ -6650,15 +6326,11 @@
       <c r="M83" t="n">
         <v>-1</v>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-1</v>
       </c>
       <c r="P83" t="n">
         <v>2</v>
@@ -6725,15 +6397,11 @@
       <c r="M84" t="n">
         <v>-1</v>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-1</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
@@ -6800,15 +6468,11 @@
       <c r="M85" t="n">
         <v>-1</v>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-1</v>
       </c>
       <c r="P85" t="n">
         <v>2</v>
@@ -6875,15 +6539,11 @@
       <c r="M86" t="n">
         <v>-1</v>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-1</v>
       </c>
       <c r="P86" t="n">
         <v>2</v>
@@ -6950,15 +6610,11 @@
       <c r="M87" t="n">
         <v>-1</v>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-1</v>
       </c>
       <c r="P87" t="n">
         <v>2</v>
@@ -7025,15 +6681,11 @@
       <c r="M88" t="n">
         <v>-1</v>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-1</v>
       </c>
       <c r="P88" t="n">
         <v>2</v>
@@ -7100,15 +6752,11 @@
       <c r="M89" t="n">
         <v>-1</v>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-1</v>
       </c>
       <c r="P89" t="n">
         <v>2</v>
@@ -7175,15 +6823,11 @@
       <c r="M90" t="n">
         <v>-1</v>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-1</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -7250,15 +6894,11 @@
       <c r="M91" t="n">
         <v>-1</v>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-1</v>
       </c>
       <c r="P91" t="n">
         <v>2</v>
@@ -7325,15 +6965,11 @@
       <c r="M92" t="n">
         <v>-1</v>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>-1</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -7400,15 +7036,11 @@
       <c r="M93" t="n">
         <v>-1</v>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>-1</v>
       </c>
       <c r="P93" t="n">
         <v>2</v>
@@ -7475,15 +7107,11 @@
       <c r="M94" t="n">
         <v>-1</v>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>-1</v>
       </c>
       <c r="P94" t="n">
         <v>2</v>
@@ -7550,15 +7178,11 @@
       <c r="M95" t="n">
         <v>-1</v>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>-1</v>
       </c>
       <c r="P95" t="n">
         <v>2</v>
@@ -7625,15 +7249,11 @@
       <c r="M96" t="n">
         <v>-1</v>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>-1</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -7700,15 +7320,11 @@
       <c r="M97" t="n">
         <v>-1</v>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>-1</v>
       </c>
       <c r="P97" t="n">
         <v>2</v>
@@ -7775,15 +7391,11 @@
       <c r="M98" t="n">
         <v>-1</v>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-1</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7850,15 +7462,11 @@
       <c r="M99" t="n">
         <v>-1</v>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>-1</v>
       </c>
       <c r="P99" t="n">
         <v>2</v>
@@ -7925,15 +7533,11 @@
       <c r="M100" t="n">
         <v>-1</v>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-1</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
@@ -8000,15 +7604,11 @@
       <c r="M101" t="n">
         <v>-1</v>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-1</v>
       </c>
       <c r="P101" t="n">
         <v>2</v>
@@ -8075,15 +7675,11 @@
       <c r="M102" t="n">
         <v>-1</v>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>-1</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
@@ -8150,15 +7746,11 @@
       <c r="M103" t="n">
         <v>-1</v>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>-1</v>
       </c>
       <c r="P103" t="n">
         <v>2</v>
@@ -8225,15 +7817,11 @@
       <c r="M104" t="n">
         <v>-1</v>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>-1</v>
       </c>
       <c r="P104" t="n">
         <v>2</v>
@@ -8300,15 +7888,11 @@
       <c r="M105" t="n">
         <v>-1</v>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-1</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -8375,15 +7959,11 @@
       <c r="M106" t="n">
         <v>-1</v>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1</v>
       </c>
       <c r="P106" t="n">
         <v>2</v>
@@ -8450,15 +8030,11 @@
       <c r="M107" t="n">
         <v>-1</v>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>-1</v>
       </c>
       <c r="P107" t="n">
         <v>2</v>
@@ -8525,15 +8101,11 @@
       <c r="M108" t="n">
         <v>-1</v>
       </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>-1</v>
       </c>
       <c r="P108" t="n">
         <v>2</v>
@@ -8600,15 +8172,11 @@
       <c r="M109" t="n">
         <v>-1</v>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-1</v>
       </c>
       <c r="P109" t="n">
         <v>2</v>
@@ -8675,15 +8243,11 @@
       <c r="M110" t="n">
         <v>-1</v>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>-1</v>
       </c>
       <c r="P110" t="n">
         <v>2</v>
@@ -8750,15 +8314,11 @@
       <c r="M111" t="n">
         <v>-1</v>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>-1</v>
       </c>
       <c r="P111" t="n">
         <v>2</v>
@@ -8825,15 +8385,11 @@
       <c r="M112" t="n">
         <v>-1</v>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>-1</v>
       </c>
       <c r="P112" t="n">
         <v>2</v>
@@ -8900,15 +8456,11 @@
       <c r="M113" t="n">
         <v>-1</v>
       </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>-1</v>
       </c>
       <c r="P113" t="n">
         <v>2</v>
@@ -8975,15 +8527,11 @@
       <c r="M114" t="n">
         <v>-1</v>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>-1</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -9050,15 +8598,11 @@
       <c r="M115" t="n">
         <v>-1</v>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>-1</v>
       </c>
       <c r="P115" t="n">
         <v>2</v>
@@ -9125,15 +8669,11 @@
       <c r="M116" t="n">
         <v>-1</v>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-1</v>
       </c>
       <c r="P116" t="n">
         <v>2</v>
@@ -9200,15 +8740,11 @@
       <c r="M117" t="n">
         <v>-1</v>
       </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O117" t="n">
+        <v>-1</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -9275,15 +8811,11 @@
       <c r="M118" t="n">
         <v>-1</v>
       </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O118" t="n">
+        <v>-1</v>
       </c>
       <c r="P118" t="n">
         <v>2</v>
@@ -9350,15 +8882,11 @@
       <c r="M119" t="n">
         <v>-1</v>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>-1</v>
       </c>
       <c r="P119" t="n">
         <v>2</v>
@@ -9425,15 +8953,11 @@
       <c r="M120" t="n">
         <v>-1</v>
       </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-1</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
@@ -9500,15 +9024,11 @@
       <c r="M121" t="n">
         <v>-1</v>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-1</v>
       </c>
       <c r="P121" t="n">
         <v>2</v>
@@ -9575,15 +9095,11 @@
       <c r="M122" t="n">
         <v>-1</v>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-1</v>
       </c>
       <c r="P122" t="n">
         <v>2</v>
@@ -9650,15 +9166,11 @@
       <c r="M123" t="n">
         <v>-1</v>
       </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>-1</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -9725,15 +9237,11 @@
       <c r="M124" t="n">
         <v>-1</v>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>-1</v>
       </c>
       <c r="P124" t="n">
         <v>2</v>
@@ -9800,15 +9308,11 @@
       <c r="M125" t="n">
         <v>-1</v>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>-1</v>
       </c>
       <c r="P125" t="n">
         <v>2</v>
@@ -9875,15 +9379,11 @@
       <c r="M126" t="n">
         <v>-1</v>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-1</v>
       </c>
       <c r="P126" t="n">
         <v>2</v>
@@ -9950,15 +9450,11 @@
       <c r="M127" t="n">
         <v>-1</v>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-1</v>
       </c>
       <c r="P127" t="n">
         <v>2</v>
@@ -10025,15 +9521,11 @@
       <c r="M128" t="n">
         <v>-1</v>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>-1</v>
       </c>
       <c r="P128" t="n">
         <v>2</v>
@@ -10100,15 +9592,11 @@
       <c r="M129" t="n">
         <v>-1</v>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>-1</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -10175,15 +9663,11 @@
       <c r="M130" t="n">
         <v>-1</v>
       </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-1</v>
       </c>
       <c r="P130" t="n">
         <v>2</v>
@@ -10250,15 +9734,11 @@
       <c r="M131" t="n">
         <v>-1</v>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>-1</v>
       </c>
       <c r="P131" t="n">
         <v>2</v>
@@ -10325,15 +9805,11 @@
       <c r="M132" t="n">
         <v>-1</v>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>-1</v>
       </c>
       <c r="P132" t="n">
         <v>2</v>
@@ -10400,15 +9876,11 @@
       <c r="M133" t="n">
         <v>-1</v>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-1</v>
       </c>
       <c r="P133" t="n">
         <v>2</v>
@@ -10475,15 +9947,11 @@
       <c r="M134" t="n">
         <v>-1</v>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-1</v>
       </c>
       <c r="P134" t="n">
         <v>2</v>
@@ -10550,15 +10018,11 @@
       <c r="M135" t="n">
         <v>-1</v>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-1</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
@@ -10625,15 +10089,11 @@
       <c r="M136" t="n">
         <v>-1</v>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-1</v>
       </c>
       <c r="P136" t="n">
         <v>2</v>
@@ -10700,15 +10160,11 @@
       <c r="M137" t="n">
         <v>-1</v>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-1</v>
       </c>
       <c r="P137" t="n">
         <v>2</v>
@@ -10775,15 +10231,11 @@
       <c r="M138" t="n">
         <v>-1</v>
       </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-1</v>
       </c>
       <c r="P138" t="n">
         <v>2</v>
@@ -10850,15 +10302,11 @@
       <c r="M139" t="n">
         <v>-1</v>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O139" t="n">
+        <v>-1</v>
       </c>
       <c r="P139" t="n">
         <v>2</v>
@@ -10925,15 +10373,11 @@
       <c r="M140" t="n">
         <v>-1</v>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O140" t="n">
+        <v>-1</v>
       </c>
       <c r="P140" t="n">
         <v>2</v>
@@ -11000,15 +10444,11 @@
       <c r="M141" t="n">
         <v>-1</v>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>-1</v>
       </c>
       <c r="P141" t="n">
         <v>2</v>
@@ -11075,15 +10515,11 @@
       <c r="M142" t="n">
         <v>-1</v>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>-1</v>
       </c>
       <c r="P142" t="n">
         <v>2</v>
@@ -11150,15 +10586,11 @@
       <c r="M143" t="n">
         <v>-1</v>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>-1</v>
       </c>
       <c r="P143" t="n">
         <v>2</v>
@@ -11225,15 +10657,11 @@
       <c r="M144" t="n">
         <v>-1</v>
       </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O144" t="n">
+        <v>-1</v>
       </c>
       <c r="P144" t="n">
         <v>2</v>
@@ -11300,15 +10728,11 @@
       <c r="M145" t="n">
         <v>-1</v>
       </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O145" t="n">
+        <v>-1</v>
       </c>
       <c r="P145" t="n">
         <v>2</v>
@@ -11375,15 +10799,11 @@
       <c r="M146" t="n">
         <v>-1</v>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O146" t="n">
+        <v>-1</v>
       </c>
       <c r="P146" t="n">
         <v>2</v>
@@ -11450,15 +10870,11 @@
       <c r="M147" t="n">
         <v>-1</v>
       </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O147" t="n">
+        <v>-1</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -11525,15 +10941,11 @@
       <c r="M148" t="n">
         <v>-1</v>
       </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>-1</v>
       </c>
       <c r="P148" t="n">
         <v>2</v>
@@ -11600,15 +11012,11 @@
       <c r="M149" t="n">
         <v>-1</v>
       </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O149" t="n">
+        <v>-1</v>
       </c>
       <c r="P149" t="n">
         <v>2</v>
@@ -11675,15 +11083,11 @@
       <c r="M150" t="n">
         <v>-1</v>
       </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O150" t="n">
+        <v>-1</v>
       </c>
       <c r="P150" t="n">
         <v>2</v>
@@ -11750,15 +11154,11 @@
       <c r="M151" t="n">
         <v>-1</v>
       </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>-1</v>
       </c>
       <c r="P151" t="n">
         <v>2</v>
@@ -11825,15 +11225,11 @@
       <c r="M152" t="n">
         <v>-1</v>
       </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O152" t="n">
+        <v>-1</v>
       </c>
       <c r="P152" t="n">
         <v>2</v>
@@ -11900,15 +11296,11 @@
       <c r="M153" t="n">
         <v>-1</v>
       </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O153" t="n">
+        <v>-1</v>
       </c>
       <c r="P153" t="n">
         <v>2</v>
@@ -11975,15 +11367,11 @@
       <c r="M154" t="n">
         <v>-1</v>
       </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>-1</v>
       </c>
       <c r="P154" t="n">
         <v>2</v>
@@ -12050,15 +11438,11 @@
       <c r="M155" t="n">
         <v>-1</v>
       </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>-1</v>
       </c>
       <c r="P155" t="n">
         <v>2</v>
@@ -12125,15 +11509,11 @@
       <c r="M156" t="n">
         <v>-1</v>
       </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O156" t="n">
+        <v>-1</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
@@ -12200,15 +11580,11 @@
       <c r="M157" t="n">
         <v>-1</v>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>-1</v>
       </c>
       <c r="P157" t="n">
         <v>2</v>
@@ -12275,15 +11651,11 @@
       <c r="M158" t="n">
         <v>-1</v>
       </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>-1</v>
       </c>
       <c r="P158" t="n">
         <v>2</v>
@@ -12350,15 +11722,11 @@
       <c r="M159" t="n">
         <v>-1</v>
       </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>-1</v>
       </c>
       <c r="P159" t="n">
         <v>2</v>
@@ -12425,15 +11793,11 @@
       <c r="M160" t="n">
         <v>-1</v>
       </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-1</v>
       </c>
       <c r="P160" t="n">
         <v>2</v>
@@ -12500,15 +11864,11 @@
       <c r="M161" t="n">
         <v>-1</v>
       </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-1</v>
       </c>
       <c r="P161" t="n">
         <v>2</v>
@@ -12575,15 +11935,11 @@
       <c r="M162" t="n">
         <v>-1</v>
       </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>-1</v>
       </c>
       <c r="P162" t="n">
         <v>2</v>
@@ -12650,15 +12006,11 @@
       <c r="M163" t="n">
         <v>-1</v>
       </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>-1</v>
       </c>
       <c r="P163" t="n">
         <v>2</v>
@@ -12725,15 +12077,11 @@
       <c r="M164" t="n">
         <v>-1</v>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>-1</v>
       </c>
       <c r="P164" t="n">
         <v>2</v>
@@ -12800,15 +12148,11 @@
       <c r="M165" t="n">
         <v>-1</v>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>-1</v>
       </c>
       <c r="P165" t="n">
         <v>2</v>
@@ -12875,15 +12219,11 @@
       <c r="M166" t="n">
         <v>-1</v>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-1</v>
       </c>
       <c r="P166" t="n">
         <v>2</v>
@@ -12950,15 +12290,11 @@
       <c r="M167" t="n">
         <v>-1</v>
       </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>-1</v>
       </c>
       <c r="P167" t="n">
         <v>2</v>
@@ -13025,15 +12361,11 @@
       <c r="M168" t="n">
         <v>-1</v>
       </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>-1</v>
       </c>
       <c r="P168" t="n">
         <v>2</v>
@@ -13100,15 +12432,11 @@
       <c r="M169" t="n">
         <v>-1</v>
       </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>-1</v>
       </c>
       <c r="P169" t="n">
         <v>2</v>
@@ -13175,15 +12503,11 @@
       <c r="M170" t="n">
         <v>-1</v>
       </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>-1</v>
       </c>
       <c r="P170" t="n">
         <v>2</v>
@@ -13250,15 +12574,11 @@
       <c r="M171" t="n">
         <v>-1</v>
       </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>-1</v>
       </c>
       <c r="P171" t="n">
         <v>2</v>
@@ -13325,15 +12645,11 @@
       <c r="M172" t="n">
         <v>-1</v>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O172" t="n">
+        <v>-1</v>
       </c>
       <c r="P172" t="n">
         <v>2</v>
@@ -13400,15 +12716,11 @@
       <c r="M173" t="n">
         <v>-1</v>
       </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O173" t="n">
+        <v>-1</v>
       </c>
       <c r="P173" t="n">
         <v>2</v>
@@ -13475,15 +12787,11 @@
       <c r="M174" t="n">
         <v>-1</v>
       </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O174" t="n">
+        <v>-1</v>
       </c>
       <c r="P174" t="n">
         <v>2</v>
@@ -13550,15 +12858,11 @@
       <c r="M175" t="n">
         <v>-1</v>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O175" t="n">
+        <v>-1</v>
       </c>
       <c r="P175" t="n">
         <v>2</v>
@@ -13625,15 +12929,11 @@
       <c r="M176" t="n">
         <v>-1</v>
       </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O176" t="n">
+        <v>-1</v>
       </c>
       <c r="P176" t="n">
         <v>2</v>
@@ -13700,15 +13000,11 @@
       <c r="M177" t="n">
         <v>-1</v>
       </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O177" t="n">
+        <v>-1</v>
       </c>
       <c r="P177" t="n">
         <v>2</v>
@@ -13775,15 +13071,11 @@
       <c r="M178" t="n">
         <v>-1</v>
       </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O178" t="n">
+        <v>-1</v>
       </c>
       <c r="P178" t="n">
         <v>2</v>
@@ -13850,15 +13142,11 @@
       <c r="M179" t="n">
         <v>-1</v>
       </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>-1</v>
       </c>
       <c r="P179" t="n">
         <v>2</v>
@@ -13925,15 +13213,11 @@
       <c r="M180" t="n">
         <v>-1</v>
       </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O180" t="n">
+        <v>-1</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -14000,15 +13284,11 @@
       <c r="M181" t="n">
         <v>-1</v>
       </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O181" t="n">
+        <v>-1</v>
       </c>
       <c r="P181" t="n">
         <v>2</v>
@@ -14075,15 +13355,11 @@
       <c r="M182" t="n">
         <v>-1</v>
       </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O182" t="n">
+        <v>-1</v>
       </c>
       <c r="P182" t="n">
         <v>2</v>
@@ -14150,15 +13426,11 @@
       <c r="M183" t="n">
         <v>-1</v>
       </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>-1</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -14225,15 +13497,11 @@
       <c r="M184" t="n">
         <v>-1</v>
       </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O184" t="n">
+        <v>-1</v>
       </c>
       <c r="P184" t="n">
         <v>2</v>
@@ -14300,15 +13568,11 @@
       <c r="M185" t="n">
         <v>-1</v>
       </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>-1</v>
       </c>
       <c r="P185" t="n">
         <v>2</v>
@@ -14375,15 +13639,11 @@
       <c r="M186" t="n">
         <v>-1</v>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O186" t="n">
+        <v>-1</v>
       </c>
       <c r="P186" t="n">
         <v>2</v>
@@ -14450,15 +13710,11 @@
       <c r="M187" t="n">
         <v>-1</v>
       </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O187" t="n">
+        <v>-1</v>
       </c>
       <c r="P187" t="n">
         <v>2</v>
@@ -14525,15 +13781,11 @@
       <c r="M188" t="n">
         <v>-1</v>
       </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O188" t="n">
+        <v>-1</v>
       </c>
       <c r="P188" t="n">
         <v>2</v>
@@ -14600,15 +13852,11 @@
       <c r="M189" t="n">
         <v>-1</v>
       </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N189" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O189" t="n">
+        <v>-1</v>
       </c>
       <c r="P189" t="n">
         <v>2</v>
@@ -14675,15 +13923,11 @@
       <c r="M190" t="n">
         <v>-1</v>
       </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N190" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O190" t="n">
+        <v>-1</v>
       </c>
       <c r="P190" t="n">
         <v>2</v>
@@ -14750,15 +13994,11 @@
       <c r="M191" t="n">
         <v>-1</v>
       </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N191" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O191" t="n">
+        <v>-1</v>
       </c>
       <c r="P191" t="n">
         <v>2</v>
@@ -14825,15 +14065,11 @@
       <c r="M192" t="n">
         <v>-1</v>
       </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N192" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O192" t="n">
+        <v>-1</v>
       </c>
       <c r="P192" t="n">
         <v>2</v>
@@ -14900,15 +14136,11 @@
       <c r="M193" t="n">
         <v>-1</v>
       </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N193" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>-1</v>
       </c>
       <c r="P193" t="n">
         <v>2</v>
@@ -14975,15 +14207,11 @@
       <c r="M194" t="n">
         <v>-1</v>
       </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N194" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-1</v>
       </c>
       <c r="P194" t="n">
         <v>2</v>
@@ -15050,15 +14278,11 @@
       <c r="M195" t="n">
         <v>-1</v>
       </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N195" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O195" t="n">
+        <v>-1</v>
       </c>
       <c r="P195" t="n">
         <v>2</v>
@@ -15125,15 +14349,11 @@
       <c r="M196" t="n">
         <v>-1</v>
       </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N196" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O196" t="n">
+        <v>-1</v>
       </c>
       <c r="P196" t="n">
         <v>2</v>
@@ -15200,15 +14420,11 @@
       <c r="M197" t="n">
         <v>-1</v>
       </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N197" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O197" t="n">
+        <v>-1</v>
       </c>
       <c r="P197" t="n">
         <v>2</v>
@@ -15275,15 +14491,11 @@
       <c r="M198" t="n">
         <v>-1</v>
       </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O198" t="n">
+        <v>-1</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
@@ -15350,15 +14562,11 @@
       <c r="M199" t="n">
         <v>-1</v>
       </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O199" t="n">
+        <v>-1</v>
       </c>
       <c r="P199" t="n">
         <v>2</v>
@@ -15425,15 +14633,11 @@
       <c r="M200" t="n">
         <v>-1</v>
       </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O200" t="n">
+        <v>-1</v>
       </c>
       <c r="P200" t="n">
         <v>2</v>
@@ -15500,15 +14704,11 @@
       <c r="M201" t="n">
         <v>-1</v>
       </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N201" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O201" t="n">
+        <v>-1</v>
       </c>
       <c r="P201" t="n">
         <v>2</v>
@@ -15575,15 +14775,11 @@
       <c r="M202" t="n">
         <v>-1</v>
       </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N202" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>-1</v>
       </c>
       <c r="P202" t="n">
         <v>2</v>
@@ -15650,15 +14846,11 @@
       <c r="M203" t="n">
         <v>-1</v>
       </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N203" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-1</v>
       </c>
       <c r="P203" t="n">
         <v>2</v>
@@ -15725,15 +14917,11 @@
       <c r="M204" t="n">
         <v>-1</v>
       </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N204" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O204" t="n">
+        <v>-1</v>
       </c>
       <c r="P204" t="n">
         <v>2</v>
@@ -15800,15 +14988,11 @@
       <c r="M205" t="n">
         <v>-1</v>
       </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N205" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O205" t="n">
+        <v>-1</v>
       </c>
       <c r="P205" t="n">
         <v>2</v>
@@ -15875,15 +15059,11 @@
       <c r="M206" t="n">
         <v>-1</v>
       </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N206" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-1</v>
       </c>
       <c r="P206" t="n">
         <v>2</v>
@@ -15950,15 +15130,11 @@
       <c r="M207" t="n">
         <v>-1</v>
       </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N207" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O207" t="n">
+        <v>-1</v>
       </c>
       <c r="P207" t="n">
         <v>2</v>
@@ -16025,15 +15201,11 @@
       <c r="M208" t="n">
         <v>-1</v>
       </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N208" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-1</v>
       </c>
       <c r="P208" t="n">
         <v>2</v>
@@ -16100,15 +15272,11 @@
       <c r="M209" t="n">
         <v>-1</v>
       </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N209" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O209" t="n">
+        <v>-1</v>
       </c>
       <c r="P209" t="n">
         <v>2</v>
@@ -16175,15 +15343,11 @@
       <c r="M210" t="n">
         <v>-1</v>
       </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O210" t="n">
+        <v>-1</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -16250,15 +15414,11 @@
       <c r="M211" t="n">
         <v>-1</v>
       </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N211" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O211" t="n">
+        <v>-1</v>
       </c>
       <c r="P211" t="n">
         <v>2</v>
@@ -16325,15 +15485,11 @@
       <c r="M212" t="n">
         <v>-1</v>
       </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O212" t="n">
+        <v>-1</v>
       </c>
       <c r="P212" t="n">
         <v>2</v>
@@ -16400,15 +15556,11 @@
       <c r="M213" t="n">
         <v>-1</v>
       </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O213" t="n">
+        <v>-1</v>
       </c>
       <c r="P213" t="n">
         <v>2</v>
@@ -16475,15 +15627,11 @@
       <c r="M214" t="n">
         <v>-1</v>
       </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N214" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O214" t="n">
+        <v>-1</v>
       </c>
       <c r="P214" t="n">
         <v>2</v>
@@ -16550,15 +15698,11 @@
       <c r="M215" t="n">
         <v>-1</v>
       </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N215" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O215" t="n">
+        <v>-1</v>
       </c>
       <c r="P215" t="n">
         <v>2</v>
@@ -16625,15 +15769,11 @@
       <c r="M216" t="n">
         <v>-1</v>
       </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N216" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O216" t="n">
+        <v>-1</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -16700,15 +15840,11 @@
       <c r="M217" t="n">
         <v>-1</v>
       </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O217" t="n">
+        <v>-1</v>
       </c>
       <c r="P217" t="n">
         <v>2</v>
@@ -16775,15 +15911,11 @@
       <c r="M218" t="n">
         <v>-1</v>
       </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N218" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O218" t="n">
+        <v>-1</v>
       </c>
       <c r="P218" t="n">
         <v>2</v>
@@ -16850,15 +15982,11 @@
       <c r="M219" t="n">
         <v>-1</v>
       </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N219" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>-1</v>
       </c>
       <c r="P219" t="n">
         <v>2</v>
@@ -16925,15 +16053,11 @@
       <c r="M220" t="n">
         <v>-1</v>
       </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O220" t="n">
+        <v>-1</v>
       </c>
       <c r="P220" t="n">
         <v>2</v>
@@ -17000,15 +16124,11 @@
       <c r="M221" t="n">
         <v>-1</v>
       </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N221" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>-1</v>
       </c>
       <c r="P221" t="n">
         <v>2</v>
@@ -17075,15 +16195,11 @@
       <c r="M222" t="n">
         <v>-1</v>
       </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N222" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O222" t="n">
+        <v>-1</v>
       </c>
       <c r="P222" t="n">
         <v>2</v>
@@ -17150,15 +16266,11 @@
       <c r="M223" t="n">
         <v>-1</v>
       </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N223" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O223" t="n">
+        <v>-1</v>
       </c>
       <c r="P223" t="n">
         <v>2</v>
@@ -17225,15 +16337,11 @@
       <c r="M224" t="n">
         <v>-1</v>
       </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N224" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O224" t="n">
+        <v>-1</v>
       </c>
       <c r="P224" t="n">
         <v>2</v>
@@ -17300,15 +16408,11 @@
       <c r="M225" t="n">
         <v>-1</v>
       </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N225" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O225" t="n">
+        <v>-1</v>
       </c>
       <c r="P225" t="n">
         <v>2</v>
@@ -17375,15 +16479,11 @@
       <c r="M226" t="n">
         <v>-1</v>
       </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N226" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O226" t="n">
+        <v>-1</v>
       </c>
       <c r="P226" t="n">
         <v>2</v>
@@ -17450,15 +16550,11 @@
       <c r="M227" t="n">
         <v>-1</v>
       </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>-1</v>
       </c>
       <c r="P227" t="n">
         <v>2</v>
@@ -17525,15 +16621,11 @@
       <c r="M228" t="n">
         <v>-1</v>
       </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N228" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O228" t="n">
+        <v>-1</v>
       </c>
       <c r="P228" t="n">
         <v>2</v>
@@ -17600,15 +16692,11 @@
       <c r="M229" t="n">
         <v>-1</v>
       </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N229" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O229" t="n">
+        <v>-1</v>
       </c>
       <c r="P229" t="n">
         <v>2</v>
@@ -17675,15 +16763,11 @@
       <c r="M230" t="n">
         <v>-1</v>
       </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N230" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>-1</v>
       </c>
       <c r="P230" t="n">
         <v>2</v>
@@ -17750,15 +16834,11 @@
       <c r="M231" t="n">
         <v>-1</v>
       </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N231" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O231" t="n">
+        <v>-1</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -17825,15 +16905,11 @@
       <c r="M232" t="n">
         <v>-1</v>
       </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N232" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>-1</v>
       </c>
       <c r="P232" t="n">
         <v>2</v>
@@ -17900,15 +16976,11 @@
       <c r="M233" t="n">
         <v>-1</v>
       </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N233" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O233" t="n">
+        <v>-1</v>
       </c>
       <c r="P233" t="n">
         <v>2</v>
@@ -17975,15 +17047,11 @@
       <c r="M234" t="n">
         <v>-1</v>
       </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N234" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O234" t="n">
+        <v>-1</v>
       </c>
       <c r="P234" t="n">
         <v>2</v>
@@ -18050,15 +17118,11 @@
       <c r="M235" t="n">
         <v>-1</v>
       </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N235" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O235" t="n">
+        <v>-1</v>
       </c>
       <c r="P235" t="n">
         <v>2</v>
@@ -18125,15 +17189,11 @@
       <c r="M236" t="n">
         <v>-1</v>
       </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N236" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O236" t="n">
+        <v>-1</v>
       </c>
       <c r="P236" t="n">
         <v>2</v>
@@ -18200,15 +17260,11 @@
       <c r="M237" t="n">
         <v>-1</v>
       </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N237" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O237" t="n">
+        <v>-1</v>
       </c>
       <c r="P237" t="n">
         <v>2</v>
@@ -18275,15 +17331,11 @@
       <c r="M238" t="n">
         <v>-1</v>
       </c>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N238" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O238" t="n">
+        <v>-1</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>
@@ -18350,15 +17402,11 @@
       <c r="M239" t="n">
         <v>-1</v>
       </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N239" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>-1</v>
       </c>
       <c r="P239" t="n">
         <v>2</v>
@@ -18425,15 +17473,11 @@
       <c r="M240" t="n">
         <v>-1</v>
       </c>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N240" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>-1</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -18500,15 +17544,11 @@
       <c r="M241" t="n">
         <v>-1</v>
       </c>
-      <c r="N241" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O241" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N241" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O241" t="n">
+        <v>-1</v>
       </c>
       <c r="P241" t="n">
         <v>2</v>
@@ -18575,15 +17615,11 @@
       <c r="M242" t="n">
         <v>-1</v>
       </c>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N242" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O242" t="n">
+        <v>-1</v>
       </c>
       <c r="P242" t="n">
         <v>2</v>
@@ -18650,15 +17686,11 @@
       <c r="M243" t="n">
         <v>-1</v>
       </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N243" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O243" t="n">
+        <v>-1</v>
       </c>
       <c r="P243" t="n">
         <v>2</v>
@@ -18725,15 +17757,11 @@
       <c r="M244" t="n">
         <v>-1</v>
       </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N244" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O244" t="n">
+        <v>-1</v>
       </c>
       <c r="P244" t="n">
         <v>2</v>
@@ -18800,15 +17828,11 @@
       <c r="M245" t="n">
         <v>-1</v>
       </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O245" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N245" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O245" t="n">
+        <v>-1</v>
       </c>
       <c r="P245" t="n">
         <v>2</v>
@@ -18875,15 +17899,11 @@
       <c r="M246" t="n">
         <v>-1</v>
       </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N246" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O246" t="n">
+        <v>-1</v>
       </c>
       <c r="P246" t="n">
         <v>2</v>
@@ -18950,15 +17970,11 @@
       <c r="M247" t="n">
         <v>-1</v>
       </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N247" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>-1</v>
       </c>
       <c r="P247" t="n">
         <v>2</v>
@@ -19025,15 +18041,11 @@
       <c r="M248" t="n">
         <v>-1</v>
       </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N248" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>-1</v>
       </c>
       <c r="P248" t="n">
         <v>2</v>
@@ -19100,15 +18112,11 @@
       <c r="M249" t="n">
         <v>-1</v>
       </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N249" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>-1</v>
       </c>
       <c r="P249" t="n">
         <v>2</v>
@@ -19175,15 +18183,11 @@
       <c r="M250" t="n">
         <v>-1</v>
       </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N250" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O250" t="n">
+        <v>-1</v>
       </c>
       <c r="P250" t="n">
         <v>2</v>
@@ -19250,15 +18254,11 @@
       <c r="M251" t="n">
         <v>-1</v>
       </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N251" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>-1</v>
       </c>
       <c r="P251" t="n">
         <v>2</v>
@@ -19325,15 +18325,11 @@
       <c r="M252" t="n">
         <v>-1</v>
       </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N252" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>-1</v>
       </c>
       <c r="P252" t="n">
         <v>2</v>
@@ -19400,15 +18396,11 @@
       <c r="M253" t="n">
         <v>-1</v>
       </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N253" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O253" t="n">
+        <v>-1</v>
       </c>
       <c r="P253" t="n">
         <v>2</v>
@@ -19475,15 +18467,11 @@
       <c r="M254" t="n">
         <v>-1</v>
       </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N254" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O254" t="n">
+        <v>-1</v>
       </c>
       <c r="P254" t="n">
         <v>2</v>
@@ -19550,15 +18538,11 @@
       <c r="M255" t="n">
         <v>-1</v>
       </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N255" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O255" t="n">
+        <v>-1</v>
       </c>
       <c r="P255" t="n">
         <v>2</v>
@@ -19625,15 +18609,11 @@
       <c r="M256" t="n">
         <v>-1</v>
       </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N256" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O256" t="n">
+        <v>-1</v>
       </c>
       <c r="P256" t="n">
         <v>2</v>
@@ -19700,15 +18680,11 @@
       <c r="M257" t="n">
         <v>-1</v>
       </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N257" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O257" t="n">
+        <v>-1</v>
       </c>
       <c r="P257" t="n">
         <v>2</v>
@@ -19775,15 +18751,11 @@
       <c r="M258" t="n">
         <v>-1</v>
       </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N258" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O258" t="n">
+        <v>-1</v>
       </c>
       <c r="P258" t="n">
         <v>2</v>
@@ -19850,15 +18822,11 @@
       <c r="M259" t="n">
         <v>-1</v>
       </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N259" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O259" t="n">
+        <v>-1</v>
       </c>
       <c r="P259" t="n">
         <v>2</v>
@@ -19925,15 +18893,11 @@
       <c r="M260" t="n">
         <v>-1</v>
       </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N260" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>-1</v>
       </c>
       <c r="P260" t="n">
         <v>2</v>
@@ -20000,15 +18964,11 @@
       <c r="M261" t="n">
         <v>-1</v>
       </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N261" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>-1</v>
       </c>
       <c r="P261" t="n">
         <v>2</v>
@@ -20075,15 +19035,11 @@
       <c r="M262" t="n">
         <v>-1</v>
       </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O262" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N262" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O262" t="n">
+        <v>-1</v>
       </c>
       <c r="P262" t="n">
         <v>2</v>
@@ -20150,15 +19106,11 @@
       <c r="M263" t="n">
         <v>-1</v>
       </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O263" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N263" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O263" t="n">
+        <v>-1</v>
       </c>
       <c r="P263" t="n">
         <v>2</v>
@@ -20225,15 +19177,11 @@
       <c r="M264" t="n">
         <v>-1</v>
       </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N264" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O264" t="n">
+        <v>-1</v>
       </c>
       <c r="P264" t="n">
         <v>2</v>
@@ -20300,15 +19248,11 @@
       <c r="M265" t="n">
         <v>-1</v>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O265" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N265" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O265" t="n">
+        <v>-1</v>
       </c>
       <c r="P265" t="n">
         <v>2</v>
@@ -20375,15 +19319,11 @@
       <c r="M266" t="n">
         <v>-1</v>
       </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N266" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O266" t="n">
+        <v>-1</v>
       </c>
       <c r="P266" t="n">
         <v>2</v>
@@ -20450,15 +19390,11 @@
       <c r="M267" t="n">
         <v>-1</v>
       </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O267" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N267" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O267" t="n">
+        <v>-1</v>
       </c>
       <c r="P267" t="n">
         <v>2</v>
@@ -20525,15 +19461,11 @@
       <c r="M268" t="n">
         <v>-1</v>
       </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N268" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O268" t="n">
+        <v>-1</v>
       </c>
       <c r="P268" t="n">
         <v>2</v>
@@ -20600,15 +19532,11 @@
       <c r="M269" t="n">
         <v>-1</v>
       </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N269" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O269" t="n">
+        <v>-1</v>
       </c>
       <c r="P269" t="n">
         <v>2</v>
@@ -20675,15 +19603,11 @@
       <c r="M270" t="n">
         <v>-1</v>
       </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N270" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O270" t="n">
+        <v>-1</v>
       </c>
       <c r="P270" t="n">
         <v>2</v>
@@ -20750,15 +19674,11 @@
       <c r="M271" t="n">
         <v>-1</v>
       </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N271" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O271" t="n">
+        <v>-1</v>
       </c>
       <c r="P271" t="n">
         <v>2</v>
@@ -20825,15 +19745,11 @@
       <c r="M272" t="n">
         <v>-1</v>
       </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N272" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O272" t="n">
+        <v>-1</v>
       </c>
       <c r="P272" t="n">
         <v>2</v>
@@ -20900,15 +19816,11 @@
       <c r="M273" t="n">
         <v>-1</v>
       </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N273" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O273" t="n">
+        <v>-1</v>
       </c>
       <c r="P273" t="n">
         <v>2</v>
@@ -20975,15 +19887,11 @@
       <c r="M274" t="n">
         <v>-1</v>
       </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O274" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N274" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O274" t="n">
+        <v>-1</v>
       </c>
       <c r="P274" t="n">
         <v>2</v>
@@ -21050,15 +19958,11 @@
       <c r="M275" t="n">
         <v>-1</v>
       </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O275" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N275" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O275" t="n">
+        <v>-1</v>
       </c>
       <c r="P275" t="n">
         <v>2</v>
@@ -21125,15 +20029,11 @@
       <c r="M276" t="n">
         <v>-1</v>
       </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N276" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O276" t="n">
+        <v>-1</v>
       </c>
       <c r="P276" t="n">
         <v>2</v>
@@ -21200,15 +20100,11 @@
       <c r="M277" t="n">
         <v>-1</v>
       </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N277" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O277" t="n">
+        <v>-1</v>
       </c>
       <c r="P277" t="n">
         <v>2</v>
@@ -21275,15 +20171,11 @@
       <c r="M278" t="n">
         <v>-1</v>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N278" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O278" t="n">
+        <v>-1</v>
       </c>
       <c r="P278" t="n">
         <v>2</v>
@@ -21350,15 +20242,11 @@
       <c r="M279" t="n">
         <v>-1</v>
       </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N279" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O279" t="n">
+        <v>-1</v>
       </c>
       <c r="P279" t="n">
         <v>2</v>
@@ -21425,15 +20313,11 @@
       <c r="M280" t="n">
         <v>-1</v>
       </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N280" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O280" t="n">
+        <v>-1</v>
       </c>
       <c r="P280" t="n">
         <v>2</v>
@@ -21500,15 +20384,11 @@
       <c r="M281" t="n">
         <v>-1</v>
       </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N281" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O281" t="n">
+        <v>-1</v>
       </c>
       <c r="P281" t="n">
         <v>2</v>
@@ -21575,15 +20455,11 @@
       <c r="M282" t="n">
         <v>-1</v>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N282" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O282" t="n">
+        <v>-1</v>
       </c>
       <c r="P282" t="n">
         <v>2</v>
@@ -21650,15 +20526,11 @@
       <c r="M283" t="n">
         <v>-1</v>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N283" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O283" t="n">
+        <v>-1</v>
       </c>
       <c r="P283" t="n">
         <v>2</v>
@@ -21725,15 +20597,11 @@
       <c r="M284" t="n">
         <v>-1</v>
       </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N284" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-1</v>
       </c>
       <c r="P284" t="n">
         <v>2</v>
@@ -21800,15 +20668,11 @@
       <c r="M285" t="n">
         <v>-1</v>
       </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N285" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O285" t="n">
+        <v>-1</v>
       </c>
       <c r="P285" t="n">
         <v>2</v>
@@ -21875,15 +20739,11 @@
       <c r="M286" t="n">
         <v>-1</v>
       </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N286" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O286" t="n">
+        <v>-1</v>
       </c>
       <c r="P286" t="n">
         <v>2</v>
@@ -21950,15 +20810,11 @@
       <c r="M287" t="n">
         <v>-1</v>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N287" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O287" t="n">
+        <v>-1</v>
       </c>
       <c r="P287" t="n">
         <v>2</v>
@@ -22025,15 +20881,11 @@
       <c r="M288" t="n">
         <v>-1</v>
       </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N288" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>-1</v>
       </c>
       <c r="P288" t="n">
         <v>2</v>
@@ -22100,15 +20952,11 @@
       <c r="M289" t="n">
         <v>-1</v>
       </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N289" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O289" t="n">
+        <v>-1</v>
       </c>
       <c r="P289" t="n">
         <v>2</v>
@@ -22175,15 +21023,11 @@
       <c r="M290" t="n">
         <v>-1</v>
       </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N290" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O290" t="n">
+        <v>-1</v>
       </c>
       <c r="P290" t="n">
         <v>2</v>
@@ -22250,15 +21094,11 @@
       <c r="M291" t="n">
         <v>-1</v>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N291" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O291" t="n">
+        <v>-1</v>
       </c>
       <c r="P291" t="n">
         <v>2</v>
@@ -22325,15 +21165,11 @@
       <c r="M292" t="n">
         <v>-1</v>
       </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N292" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O292" t="n">
+        <v>-1</v>
       </c>
       <c r="P292" t="n">
         <v>2</v>
@@ -22400,15 +21236,11 @@
       <c r="M293" t="n">
         <v>-1</v>
       </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N293" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O293" t="n">
+        <v>-1</v>
       </c>
       <c r="P293" t="n">
         <v>2</v>
@@ -22475,15 +21307,11 @@
       <c r="M294" t="n">
         <v>-1</v>
       </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N294" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O294" t="n">
+        <v>-1</v>
       </c>
       <c r="P294" t="n">
         <v>2</v>
@@ -22550,15 +21378,11 @@
       <c r="M295" t="n">
         <v>-1</v>
       </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N295" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O295" t="n">
+        <v>-1</v>
       </c>
       <c r="P295" t="n">
         <v>2</v>
@@ -22625,15 +21449,11 @@
       <c r="M296" t="n">
         <v>-1</v>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N296" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O296" t="n">
+        <v>-1</v>
       </c>
       <c r="P296" t="n">
         <v>2</v>
@@ -22700,15 +21520,11 @@
       <c r="M297" t="n">
         <v>-1</v>
       </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N297" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O297" t="n">
+        <v>-1</v>
       </c>
       <c r="P297" t="n">
         <v>2</v>
@@ -22775,15 +21591,11 @@
       <c r="M298" t="n">
         <v>-1</v>
       </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N298" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O298" t="n">
+        <v>-1</v>
       </c>
       <c r="P298" t="n">
         <v>2</v>
@@ -22850,15 +21662,11 @@
       <c r="M299" t="n">
         <v>-1</v>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N299" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O299" t="n">
+        <v>-1</v>
       </c>
       <c r="P299" t="n">
         <v>2</v>
@@ -22925,15 +21733,11 @@
       <c r="M300" t="n">
         <v>-1</v>
       </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N300" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O300" t="n">
+        <v>-1</v>
       </c>
       <c r="P300" t="n">
         <v>2</v>
@@ -23000,15 +21804,11 @@
       <c r="M301" t="n">
         <v>-1</v>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N301" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O301" t="n">
+        <v>-1</v>
       </c>
       <c r="P301" t="n">
         <v>2</v>
@@ -23075,15 +21875,11 @@
       <c r="M302" t="n">
         <v>-1</v>
       </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N302" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O302" t="n">
+        <v>-1</v>
       </c>
       <c r="P302" t="n">
         <v>2</v>
@@ -23150,15 +21946,11 @@
       <c r="M303" t="n">
         <v>-1</v>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N303" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O303" t="n">
+        <v>-1</v>
       </c>
       <c r="P303" t="n">
         <v>2</v>
@@ -23225,15 +22017,11 @@
       <c r="M304" t="n">
         <v>-1</v>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N304" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O304" t="n">
+        <v>-1</v>
       </c>
       <c r="P304" t="n">
         <v>2</v>
@@ -23300,15 +22088,11 @@
       <c r="M305" t="n">
         <v>-1</v>
       </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N305" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O305" t="n">
+        <v>-1</v>
       </c>
       <c r="P305" t="n">
         <v>2</v>
@@ -23375,15 +22159,11 @@
       <c r="M306" t="n">
         <v>-1</v>
       </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N306" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O306" t="n">
+        <v>-1</v>
       </c>
       <c r="P306" t="n">
         <v>2</v>
@@ -23450,15 +22230,11 @@
       <c r="M307" t="n">
         <v>-1</v>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O307" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N307" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O307" t="n">
+        <v>-1</v>
       </c>
       <c r="P307" t="n">
         <v>2</v>
@@ -23525,15 +22301,11 @@
       <c r="M308" t="n">
         <v>-1</v>
       </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N308" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O308" t="n">
+        <v>-1</v>
       </c>
       <c r="P308" t="n">
         <v>2</v>
@@ -23600,15 +22372,11 @@
       <c r="M309" t="n">
         <v>-1</v>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N309" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O309" t="n">
+        <v>-1</v>
       </c>
       <c r="P309" t="n">
         <v>2</v>
@@ -23675,15 +22443,11 @@
       <c r="M310" t="n">
         <v>-1</v>
       </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N310" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O310" t="n">
+        <v>-1</v>
       </c>
       <c r="P310" t="n">
         <v>2</v>
@@ -23750,15 +22514,11 @@
       <c r="M311" t="n">
         <v>-1</v>
       </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O311" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N311" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O311" t="n">
+        <v>-1</v>
       </c>
       <c r="P311" t="n">
         <v>2</v>
@@ -23825,15 +22585,11 @@
       <c r="M312" t="n">
         <v>-1</v>
       </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O312" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N312" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O312" t="n">
+        <v>-1</v>
       </c>
       <c r="P312" t="n">
         <v>2</v>
@@ -23900,15 +22656,11 @@
       <c r="M313" t="n">
         <v>-1</v>
       </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N313" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O313" t="n">
+        <v>-1</v>
       </c>
       <c r="P313" t="n">
         <v>2</v>
@@ -23975,15 +22727,11 @@
       <c r="M314" t="n">
         <v>-1</v>
       </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N314" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O314" t="n">
+        <v>-1</v>
       </c>
       <c r="P314" t="n">
         <v>2</v>
@@ -24050,15 +22798,11 @@
       <c r="M315" t="n">
         <v>-1</v>
       </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O315" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N315" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O315" t="n">
+        <v>-1</v>
       </c>
       <c r="P315" t="n">
         <v>2</v>
@@ -24125,15 +22869,11 @@
       <c r="M316" t="n">
         <v>-1</v>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N316" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O316" t="n">
+        <v>-1</v>
       </c>
       <c r="P316" t="n">
         <v>2</v>
@@ -24200,15 +22940,11 @@
       <c r="M317" t="n">
         <v>-1</v>
       </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N317" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O317" t="n">
+        <v>-1</v>
       </c>
       <c r="P317" t="n">
         <v>2</v>
@@ -24275,15 +23011,11 @@
       <c r="M318" t="n">
         <v>-1</v>
       </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N318" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O318" t="n">
+        <v>-1</v>
       </c>
       <c r="P318" t="n">
         <v>2</v>
@@ -24350,15 +23082,11 @@
       <c r="M319" t="n">
         <v>-1</v>
       </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O319" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N319" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O319" t="n">
+        <v>-1</v>
       </c>
       <c r="P319" t="n">
         <v>2</v>
@@ -24425,15 +23153,11 @@
       <c r="M320" t="n">
         <v>-1</v>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O320" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N320" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O320" t="n">
+        <v>-1</v>
       </c>
       <c r="P320" t="n">
         <v>2</v>
@@ -24500,15 +23224,11 @@
       <c r="M321" t="n">
         <v>-1</v>
       </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N321" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O321" t="n">
+        <v>-1</v>
       </c>
       <c r="P321" t="n">
         <v>2</v>
@@ -24575,15 +23295,11 @@
       <c r="M322" t="n">
         <v>-1</v>
       </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O322" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N322" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O322" t="n">
+        <v>-1</v>
       </c>
       <c r="P322" t="n">
         <v>2</v>
@@ -24650,15 +23366,11 @@
       <c r="M323" t="n">
         <v>-1</v>
       </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N323" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O323" t="n">
+        <v>-1</v>
       </c>
       <c r="P323" t="n">
         <v>2</v>
@@ -24725,15 +23437,11 @@
       <c r="M324" t="n">
         <v>-1</v>
       </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N324" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O324" t="n">
+        <v>-1</v>
       </c>
       <c r="P324" t="n">
         <v>2</v>
@@ -24800,15 +23508,11 @@
       <c r="M325" t="n">
         <v>-1</v>
       </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O325" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N325" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O325" t="n">
+        <v>-1</v>
       </c>
       <c r="P325" t="n">
         <v>2</v>
@@ -24875,15 +23579,11 @@
       <c r="M326" t="n">
         <v>-1</v>
       </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O326" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N326" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O326" t="n">
+        <v>-1</v>
       </c>
       <c r="P326" t="n">
         <v>2</v>
@@ -24950,15 +23650,11 @@
       <c r="M327" t="n">
         <v>-1</v>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N327" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O327" t="n">
+        <v>-1</v>
       </c>
       <c r="P327" t="n">
         <v>2</v>
@@ -25025,15 +23721,11 @@
       <c r="M328" t="n">
         <v>-1</v>
       </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N328" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O328" t="n">
+        <v>-1</v>
       </c>
       <c r="P328" t="n">
         <v>2</v>
@@ -25100,15 +23792,11 @@
       <c r="M329" t="n">
         <v>-1</v>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O329" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N329" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O329" t="n">
+        <v>-1</v>
       </c>
       <c r="P329" t="n">
         <v>2</v>
@@ -25175,15 +23863,11 @@
       <c r="M330" t="n">
         <v>-1</v>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O330" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N330" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O330" t="n">
+        <v>-1</v>
       </c>
       <c r="P330" t="n">
         <v>2</v>
@@ -25250,15 +23934,11 @@
       <c r="M331" t="n">
         <v>-1</v>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N331" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O331" t="n">
+        <v>-1</v>
       </c>
       <c r="P331" t="n">
         <v>2</v>
@@ -25325,15 +24005,11 @@
       <c r="M332" t="n">
         <v>-1</v>
       </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N332" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O332" t="n">
+        <v>-1</v>
       </c>
       <c r="P332" t="n">
         <v>2</v>
@@ -25400,15 +24076,11 @@
       <c r="M333" t="n">
         <v>-1</v>
       </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O333" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N333" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O333" t="n">
+        <v>-1</v>
       </c>
       <c r="P333" t="n">
         <v>2</v>
@@ -25475,15 +24147,11 @@
       <c r="M334" t="n">
         <v>-1</v>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O334" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N334" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O334" t="n">
+        <v>-1</v>
       </c>
       <c r="P334" t="n">
         <v>2</v>
@@ -25550,15 +24218,11 @@
       <c r="M335" t="n">
         <v>-1</v>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O335" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N335" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O335" t="n">
+        <v>-1</v>
       </c>
       <c r="P335" t="n">
         <v>2</v>
@@ -25625,15 +24289,11 @@
       <c r="M336" t="n">
         <v>-1</v>
       </c>
-      <c r="N336" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O336" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N336" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O336" t="n">
+        <v>-1</v>
       </c>
       <c r="P336" t="n">
         <v>2</v>
@@ -25700,15 +24360,11 @@
       <c r="M337" t="n">
         <v>-1</v>
       </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O337" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N337" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O337" t="n">
+        <v>-1</v>
       </c>
       <c r="P337" t="n">
         <v>2</v>
@@ -25775,15 +24431,11 @@
       <c r="M338" t="n">
         <v>-1</v>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O338" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N338" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O338" t="n">
+        <v>-1</v>
       </c>
       <c r="P338" t="n">
         <v>2</v>
@@ -25850,15 +24502,11 @@
       <c r="M339" t="n">
         <v>-1</v>
       </c>
-      <c r="N339" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O339" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N339" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O339" t="n">
+        <v>-1</v>
       </c>
       <c r="P339" t="n">
         <v>2</v>
@@ -25925,15 +24573,11 @@
       <c r="M340" t="n">
         <v>-1</v>
       </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O340" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N340" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O340" t="n">
+        <v>-1</v>
       </c>
       <c r="P340" t="n">
         <v>2</v>
@@ -26000,15 +24644,11 @@
       <c r="M341" t="n">
         <v>-1</v>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N341" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O341" t="n">
+        <v>-1</v>
       </c>
       <c r="P341" t="n">
         <v>2</v>
@@ -26075,15 +24715,11 @@
       <c r="M342" t="n">
         <v>-1</v>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O342" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N342" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O342" t="n">
+        <v>-1</v>
       </c>
       <c r="P342" t="n">
         <v>2</v>
@@ -26150,15 +24786,11 @@
       <c r="M343" t="n">
         <v>-1</v>
       </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N343" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O343" t="n">
+        <v>-1</v>
       </c>
       <c r="P343" t="n">
         <v>2</v>
@@ -26225,15 +24857,11 @@
       <c r="M344" t="n">
         <v>-1</v>
       </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O344" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N344" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O344" t="n">
+        <v>-1</v>
       </c>
       <c r="P344" t="n">
         <v>2</v>
@@ -26300,15 +24928,11 @@
       <c r="M345" t="n">
         <v>-1</v>
       </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N345" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O345" t="n">
+        <v>-1</v>
       </c>
       <c r="P345" t="n">
         <v>2</v>
@@ -26375,15 +24999,11 @@
       <c r="M346" t="n">
         <v>-1</v>
       </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N346" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O346" t="n">
+        <v>-1</v>
       </c>
       <c r="P346" t="n">
         <v>2</v>
@@ -26450,15 +25070,11 @@
       <c r="M347" t="n">
         <v>-1</v>
       </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N347" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O347" t="n">
+        <v>-1</v>
       </c>
       <c r="P347" t="n">
         <v>2</v>
@@ -26525,15 +25141,11 @@
       <c r="M348" t="n">
         <v>-1</v>
       </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O348" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N348" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O348" t="n">
+        <v>-1</v>
       </c>
       <c r="P348" t="n">
         <v>2</v>
@@ -26600,15 +25212,11 @@
       <c r="M349" t="n">
         <v>-1</v>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N349" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O349" t="n">
+        <v>-1</v>
       </c>
       <c r="P349" t="n">
         <v>2</v>
@@ -26675,15 +25283,11 @@
       <c r="M350" t="n">
         <v>-1</v>
       </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O350" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N350" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O350" t="n">
+        <v>-1</v>
       </c>
       <c r="P350" t="n">
         <v>2</v>
@@ -26750,15 +25354,11 @@
       <c r="M351" t="n">
         <v>-1</v>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N351" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O351" t="n">
+        <v>-1</v>
       </c>
       <c r="P351" t="n">
         <v>2</v>
@@ -26825,15 +25425,11 @@
       <c r="M352" t="n">
         <v>-1</v>
       </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N352" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O352" t="n">
+        <v>-1</v>
       </c>
       <c r="P352" t="n">
         <v>2</v>
@@ -26900,15 +25496,11 @@
       <c r="M353" t="n">
         <v>-1</v>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N353" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O353" t="n">
+        <v>-1</v>
       </c>
       <c r="P353" t="n">
         <v>2</v>
@@ -26975,15 +25567,11 @@
       <c r="M354" t="n">
         <v>-1</v>
       </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N354" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O354" t="n">
+        <v>-1</v>
       </c>
       <c r="P354" t="n">
         <v>2</v>
@@ -27050,15 +25638,11 @@
       <c r="M355" t="n">
         <v>-1</v>
       </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="N355" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O355" t="n">
+        <v>-1</v>
       </c>
       <c r="P355" t="n">
         <v>2</v>
